--- a/docs/planning/QA엑셀-v1/남다슬/QA 담양 중대재해 안전보건교육 남다슬.xlsx
+++ b/docs/planning/QA엑셀-v1/남다슬/QA 담양 중대재해 안전보건교육 남다슬.xlsx
@@ -14,13 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 자체·채용시·기타" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 이수현황" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 공문·결재 이력" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 계정별 차이" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 부서 담당자·다시 로그인" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_정보" sheetId="9" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1 근로자 명단'!$A$3:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1 근로자 명단'!$A$3:$I$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'1 근로자 명단'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2 정기교육(집합)'!$A$3:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2 정기교육(집합)'!$A$3:$I$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'2 정기교육(집합)'!$3:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3 자체·채용시·기타'!$A$3:$I$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'3 자체·채용시·기타'!$3:$3</definedName>
@@ -28,8 +28,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'4 이수현황'!$3:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'5 공문·결재 이력'!$A$3:$I$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'5 공문·결재 이력'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'6 계정별 차이'!$A$3:$I$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'6 계정별 차이'!$3:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'6 부서 담당자·다시 로그인'!$A$3:$I$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'6 부서 담당자·다시 로그인'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -40,7 +40,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,9 +64,9 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="000563C1"/>
       <sz val="10.5"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -119,6 +119,12 @@
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00A6A6A6"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
       <sz val="10.5"/>
     </font>
   </fonts>
@@ -295,7 +301,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -793,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -849,15 +855,15 @@
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>이 파일</t>
+          <t>내 계정</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>근로자 명단 → 교육 등록 → 참석자 등록부 → 교육 종료 → 이수현황 → 공문까지 봅니다. 이수 기록은 참석자를 등록할 때가 아니라 [교육 종료 처리]를 눌러야 생깁니다.</t>
+          <t>QA박안전2 (재난안전과 담당자) · QA하정수2 (내 부서 건설과 담당 공무원)</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -867,15 +873,15 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>줄 수</t>
+          <t>이 파일</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>58줄</t>
+          <t>근로자 명단 → 교육 등록 → 참석자 등록부 → 교육 종료 → 이수현황 → 공문까지 봅니다. 이수 기록은 참석자를 등록할 때가 아니라 [교육 종료 처리]를 눌러야 생깁니다. 내가 만든 «남다슬_…» 근로자·교육만 고치고 지웁니다.</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -888,12 +894,12 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>시트</t>
+          <t>줄 수</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>1 근로자 명단 → 2 정기교육(집합) → 3 자체·채용시·기타 → 4 이수현황 → 5 공문·결재 이력 → 6 계정별 차이</t>
+          <t>58줄</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -906,12 +912,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>테스트 주소</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>(배포 주소를 받으면 채웁니다)</t>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>1 근로자 명단 → 2 정기교육(집합) → 3 자체·채용시·기타 → 4 이수현황 → 5 공문·결재 이력 → 6 부서 담당자·다시 로그인</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -924,10 +930,14 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>브라우저</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
+          <t>테스트 주소</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>https://safety.damyang.go.kr/login</t>
+        </is>
+      </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
@@ -938,7 +948,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>기기</t>
+          <t>브라우저</t>
         </is>
       </c>
       <c r="B10" s="7" t="n"/>
@@ -952,10 +962,10 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>시작한 날</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
+          <t>기기</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
@@ -963,82 +973,78 @@
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>시작한 날</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>이렇게 하면 됩니다</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>① 브라우저로 위 «테스트 주소»를 엽니다. 시트마다 맨 위에 «새 탭에서 시작» 또는 «같은 탭에서 이어서»가 적혀 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1">
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>② 화면 오른쪽 위 이름을 눌러 «누구로» 칸의 사람으로 바꿉니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1">
+          <t>① 위 «테스트 주소»에서 받은 아이디·비밀번호로 로그인합니다. 로그인하면 통합 현황 화면으로 갑니다. 5번 틀리면 계정이 잠깁니다 — 담당 개발자에게 풀어 달라고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>③ «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
+          <t>② 내 계정 두 개를 창 두 개에 따로 로그인해 둡니다 — 일반 창에는 QA박안전2(재난안전과), 시크릿 창(Ctrl + Shift + N · 맥 Cmd + Shift + N)에는 QA하정수2(담당 공무원). 두 창을 나란히 두면 계정을 바꿀 필요가 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+          <t>③ «누구로» 칸에 적힌 계정의 창에서 «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>⑤ 실패·오류·문의면 «메모»에 한 줄 적고, 필요하면 «사진» 칸에 화면 캡처를 붙여넣습니다.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>결과 고르는 법</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>결과</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>이럴 때 고르세요</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -1049,14 +1055,14 @@
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>실패</t>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>성공</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
+          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
@@ -1067,14 +1073,14 @@
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>오류</t>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>실패</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
+          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -1085,14 +1091,14 @@
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>보류</t>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>오류</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
+          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
@@ -1103,14 +1109,14 @@
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>보류</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
+          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
@@ -1121,14 +1127,14 @@
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>문의</t>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
@@ -1138,256 +1144,216 @@
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>사진 붙이는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
+          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
+          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
           <t>• 사진은 떠 있는 그대로 두세요(«셀에 배치»로 넣으면 취합할 때 꺼내지 못합니다).</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>누구로 — 계정 바꾸는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="21" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>• 화면 오른쪽 위 이름을 누르면 사람 목록이 나옵니다. «누구로» 칸의 이름을 누르면 바뀝니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>누구로 — 내 계정 두 개</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>• 계정은 두 개뿐입니다. «누구로» 칸에 계정 이름과 권한이 함께 적혀 있습니다. 비밀번호는 따로 받습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>누구</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>권한</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>볼 수 있는 것</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>주로 하는 것</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>재난안전과 담당자</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>대부분 이 계정 — 등록·확인·공문</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="5" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA박안전2</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소 담당자</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서 일만 한다</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n"/>
+          <t>재난안전과 담당자</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>모든 부서 · «내 할일»은 전체</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>전 부서 등록·수정 · 확인 · 상신 · 독촉 — 대부분 이 계정</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="5" t="n"/>
     </row>
-    <row r="40" ht="22" customHeight="1">
+    <row r="40" ht="51" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>정환경</t>
+          <t>QA하정수2</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>환경과 담당자</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>남의 부서 것을 못 건드리는지 볼 때</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n"/>
+          <t>담당 공무원 (내 부서: 건설과)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>업무 화면은 전 부서, «내 할일»은 나에게 지정된 것만, 위험성평가 부서별 조치표·교육 이수현황은 내 부서만</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>내 부서 일 · 남의 부서 것을 못 건드리는지 확인</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="5" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>오순환</t>
+          <t>QA시스템관리</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소장</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서를 보고 재촉한다</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n"/>
+          <t>시스템 관리자 (김유석만)</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 메뉴</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 파일 · 공문 반려(결재 대행)</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="5" t="n"/>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>김중대</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>중대재해팀장</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>공문 결재선(검토)을 볼 때</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>재난안전과장</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다 — 등록 버튼이 없는 게 정상</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>김담양</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>군수</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="5" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>같은 서버를 6명이 함께 씁니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>• 내가 만드는 것(교육 · 근로자 · 문서 · 위원 등)은 이름 앞에 내 이름을 붙입니다 — 예: «남다슬_집합교육». 그래야 내 것을 찾기 쉽습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>• 다른 사람이 만든 것은 고치거나 지우지 않습니다. QA박안전2 계정에는 남의 것도 보이는데, 정상입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>• 건수·이수율 같은 숫자는 다른 사람이 작업하는 동안 바뀔 수 있습니다. 숫자가 안 맞으면 새로고침해서 한 번 더 보고, 그래도 다르면 «실패».</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>알아 두면 좋은 것 (결함이 아닙니다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="21" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>• 오늘 날짜가 2026-07-16 으로 고정돼 있습니다. 기한·D-day는 이 날 기준입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="21" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>• 입력한 데이터는 그 브라우저 탭에만 남습니다. 새 탭을 열면 처음 상태로 돌아갑니다(새로고침은 괜찮습니다).</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>• 파일 첨부는 파일 이름만 남습니다. 실제 파일을 열거나 받을 수는 없습니다.</t>
+          <t>• 기한·D-day는 서버의 오늘 날짜 기준입니다.</t>
         </is>
       </c>
     </row>
@@ -1401,85 +1367,110 @@
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>• 과장·군수에게 등록·수정 버튼이 없는 것, 결재 승인·반려 버튼이 없는 것(결재는 온나라에서 합니다)은 정상입니다.</t>
+          <t>• «이러면 성공»의 «» 안 문구와 화면 글자가 조금 다르고(띄어쓰기·마침표·어순) 뜻이 같으면 «문의»로 고르고 화면 문구를 메모에 적습니다.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>• 2025년 자료는 실제 문서이고, 2026년 자료는 «예시 자료»입니다.</t>
+          <t>• 온나라 연계 전까지 결재는 시스템 안에서 끝납니다 — 상신하면 바로 «결재완료»가 되고 «내부 처리»로 표시됩니다. 결재자가 로그인해 승인할 일은 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>• ---</t>
+          <t>• 로그인은 30분이 지나면 끊깁니다(작업 중이어도). 다시 로그인하고 이어서 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>• 독촉·재촉 알림은 실제 직원에게 가고 되돌릴 수 없습니다. 내 부서 건만 1건씩 누릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>• 과장·팀장이 담당자를 지정하는 흐름과 «내 할일»의 ‹자기 부서 전체› 보기는 과장 계정이 없어 이번 QA 범위 밖입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>• 순서를 놓쳤거나 확인할 자료가 서버에 없으면 «확인 불가»를 고르고 메모에 이유를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A30:H30"/>
+  <mergeCells count="51">
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A49:H49"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="D40:E40"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F38:H38"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B25:H25"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="A50:H50"/>
-    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="B12:H12"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A47:H47"/>
     <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="B23:H23"/>
     <mergeCell ref="A17:H17"/>
+    <mergeCell ref="D39:E39"/>
     <mergeCell ref="B8:H8"/>
-    <mergeCell ref="E40:H40"/>
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="A52:H52"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"크롬,엣지,웨일,사파리,파이어폭스,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"윈도우 PC,맥,태블릿,휴대폰"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1579,36 +1570,36 @@
         </is>
       </c>
       <c r="B5" s="21">
-        <f>COUNTA('1 근로자 명단'!$A$4:$A$12)</f>
-        <v>9</v>
+        <f>COUNTA('1 근로자 명단'!$A$4:$A$13)</f>
+        <v>10</v>
       </c>
       <c r="C5" s="21">
-        <f>COUNTIF('1 근로자 명단'!$G$4:$G$12,"성공")</f>
+        <f>COUNTIF('1 근로자 명단'!$G$4:$G$13,"성공")</f>
         <v>0</v>
       </c>
       <c r="D5" s="21">
-        <f>COUNTIF('1 근로자 명단'!$G$4:$G$12,"실패")</f>
+        <f>COUNTIF('1 근로자 명단'!$G$4:$G$13,"실패")</f>
         <v>0</v>
       </c>
       <c r="E5" s="21">
-        <f>COUNTIF('1 근로자 명단'!$G$4:$G$12,"오류")</f>
+        <f>COUNTIF('1 근로자 명단'!$G$4:$G$13,"오류")</f>
         <v>0</v>
       </c>
       <c r="F5" s="21">
-        <f>COUNTIF('1 근로자 명단'!$G$4:$G$12,"보류")</f>
+        <f>COUNTIF('1 근로자 명단'!$G$4:$G$13,"보류")</f>
         <v>0</v>
       </c>
       <c r="G5" s="21">
-        <f>COUNTIF('1 근로자 명단'!$G$4:$G$12,"확인 불가")</f>
+        <f>COUNTIF('1 근로자 명단'!$G$4:$G$13,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H5" s="21">
-        <f>COUNTIF('1 근로자 명단'!$G$4:$G$12,"문의")</f>
+        <f>COUNTIF('1 근로자 명단'!$G$4:$G$13,"문의")</f>
         <v>0</v>
       </c>
       <c r="I5" s="21">
-        <f>COUNTBLANK('1 근로자 명단'!$G$4:$G$12)</f>
-        <v>9</v>
+        <f>COUNTBLANK('1 근로자 명단'!$G$4:$G$13)</f>
+        <v>10</v>
       </c>
       <c r="J5" s="22">
         <f>IF(B5=0,0,(B5-I5)/B5)</f>
@@ -1622,36 +1613,36 @@
         </is>
       </c>
       <c r="B6" s="21">
-        <f>COUNTA('2 정기교육(집합)'!$A$4:$A$18)</f>
-        <v>15</v>
+        <f>COUNTA('2 정기교육(집합)'!$A$4:$A$19)</f>
+        <v>16</v>
       </c>
       <c r="C6" s="21">
-        <f>COUNTIF('2 정기교육(집합)'!$G$4:$G$18,"성공")</f>
+        <f>COUNTIF('2 정기교육(집합)'!$G$4:$G$19,"성공")</f>
         <v>0</v>
       </c>
       <c r="D6" s="21">
-        <f>COUNTIF('2 정기교육(집합)'!$G$4:$G$18,"실패")</f>
+        <f>COUNTIF('2 정기교육(집합)'!$G$4:$G$19,"실패")</f>
         <v>0</v>
       </c>
       <c r="E6" s="21">
-        <f>COUNTIF('2 정기교육(집합)'!$G$4:$G$18,"오류")</f>
+        <f>COUNTIF('2 정기교육(집합)'!$G$4:$G$19,"오류")</f>
         <v>0</v>
       </c>
       <c r="F6" s="21">
-        <f>COUNTIF('2 정기교육(집합)'!$G$4:$G$18,"보류")</f>
+        <f>COUNTIF('2 정기교육(집합)'!$G$4:$G$19,"보류")</f>
         <v>0</v>
       </c>
       <c r="G6" s="21">
-        <f>COUNTIF('2 정기교육(집합)'!$G$4:$G$18,"확인 불가")</f>
+        <f>COUNTIF('2 정기교육(집합)'!$G$4:$G$19,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H6" s="21">
-        <f>COUNTIF('2 정기교육(집합)'!$G$4:$G$18,"문의")</f>
+        <f>COUNTIF('2 정기교육(집합)'!$G$4:$G$19,"문의")</f>
         <v>0</v>
       </c>
       <c r="I6" s="21">
-        <f>COUNTBLANK('2 정기교육(집합)'!$G$4:$G$18)</f>
-        <v>15</v>
+        <f>COUNTBLANK('2 정기교육(집합)'!$G$4:$G$19)</f>
+        <v>16</v>
       </c>
       <c r="J6" s="22">
         <f>IF(B6=0,0,(B6-I6)/B6)</f>
@@ -1790,40 +1781,40 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>6 계정별 차이</t>
+          <t>6 부서 담당자·다시 로그인</t>
         </is>
       </c>
       <c r="B10" s="21">
-        <f>COUNTA('6 계정별 차이'!$A$4:$A$8)</f>
-        <v>5</v>
+        <f>COUNTA('6 부서 담당자·다시 로그인'!$A$4:$A$6)</f>
+        <v>3</v>
       </c>
       <c r="C10" s="21">
-        <f>COUNTIF('6 계정별 차이'!$G$4:$G$8,"성공")</f>
+        <f>COUNTIF('6 부서 담당자·다시 로그인'!$G$4:$G$6,"성공")</f>
         <v>0</v>
       </c>
       <c r="D10" s="21">
-        <f>COUNTIF('6 계정별 차이'!$G$4:$G$8,"실패")</f>
+        <f>COUNTIF('6 부서 담당자·다시 로그인'!$G$4:$G$6,"실패")</f>
         <v>0</v>
       </c>
       <c r="E10" s="21">
-        <f>COUNTIF('6 계정별 차이'!$G$4:$G$8,"오류")</f>
+        <f>COUNTIF('6 부서 담당자·다시 로그인'!$G$4:$G$6,"오류")</f>
         <v>0</v>
       </c>
       <c r="F10" s="21">
-        <f>COUNTIF('6 계정별 차이'!$G$4:$G$8,"보류")</f>
+        <f>COUNTIF('6 부서 담당자·다시 로그인'!$G$4:$G$6,"보류")</f>
         <v>0</v>
       </c>
       <c r="G10" s="21">
-        <f>COUNTIF('6 계정별 차이'!$G$4:$G$8,"확인 불가")</f>
+        <f>COUNTIF('6 부서 담당자·다시 로그인'!$G$4:$G$6,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H10" s="21">
-        <f>COUNTIF('6 계정별 차이'!$G$4:$G$8,"문의")</f>
+        <f>COUNTIF('6 부서 담당자·다시 로그인'!$G$4:$G$6,"문의")</f>
         <v>0</v>
       </c>
       <c r="I10" s="21">
-        <f>COUNTBLANK('6 계정별 차이'!$G$4:$G$8)</f>
-        <v>5</v>
+        <f>COUNTBLANK('6 부서 담당자·다시 로그인'!$G$4:$G$6)</f>
+        <v>3</v>
       </c>
       <c r="J10" s="22">
         <f>IF(B10=0,0,(B10-I10)/B10)</f>
@@ -1913,11 +1904,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -1934,10 +1925,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 새 탭에서 시작하세요. 1~5번 시트는 이 탭 하나에서 이어서 합니다.</t>
+          <t>🗂 QA박안전2 창(재난안전과)과 QA하정수2 창(내 부서)을 씁니다. 여기서 만드는 «남다슬_근로자01»·«남다슬_관리감독자»와 10번에서 올리는 4명을 뒤 시트에서 계속 씁니다. 10번에서 올라가는 4명은 이름이 정해져 있어 다른 부서에도 같은 이름이 있습니다 — 고를 때는 부서 조건을 내 부서에 겁니다.</t>
         </is>
       </c>
     </row>
@@ -1988,13 +1979,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="28" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2009,25 +2000,26 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>검색·부서·구분·고용형태 조건을 하나씩 건다 → [필터 초기화]</t>
+          <t>① 검색·부서·구분·고용형태 조건을 하나씩 건다
+② [필터 초기화]</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>조건마다 건수가 바뀌고 초기화하면 전체로 돌아온다</t>
+          <t>조건마다 건수가 바뀌고, 초기화하면 전체 건수로 돌아온다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="51" customHeight="1">
+    <row r="5" ht="81" customHeight="1">
       <c r="A5" s="28" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -2042,25 +2034,27 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[＋ 직접 등록] → 이름 QA_근로자01 · 부서 물순환사업소 · 구분 근로자 · 계약직 · 채용일 2026-07-01 · 계약기간 6 → [등록]</t>
+          <t>① [＋ 직접 등록]
+② 이름 «남다슬_근로자01» · 부서는 [조직도]에서 내 부서(건설과) · 구분 비사무직(현업) · 고용형태 기간제 · 채용일 오늘 · 계약기간 6
+③ [등록]</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>«QA_근로자01 근로자 등록 완료»가 뜨고 목록에 보인다</t>
+          <t>«남다슬_근로자01 근로자 등록 완료»가 뜨고 목록에 부서 건설과 줄로 보인다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="96" customHeight="1">
       <c r="A6" s="28" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -2075,25 +2069,28 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>이름 비움 / 채용일 비움 / 계약직인데 계약기간 비움 — 각각 [등록]</t>
+          <t>[＋ 직접 등록]에서 ① 이름을 비우고 [등록]
+② 이름 «남다슬_근로자03»을 넣고 채용일을 비운 뒤 [등록]
+③ 채용일을 오늘로 되돌리고 고용형태 기간제·계약기간을 비운 뒤 [등록]
+④ [취소]</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>무엇을 넣으라고 알려 주고 등록되지 않는다(«등록 완료»가 뜨면 실패)</t>
+          <t>차례로 «이름을 입력하세요.» «채용일을 입력하세요.» «계약기간을 0보다 크게 입력하세요 — …»가 뜨고 등록되지 않는다(«등록 완료»가 뜨면 실패)</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="28" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -2103,30 +2100,30 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>관리감독자 지정일 넣기</t>
+          <t>관리감독자 등록</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>관리감독자 줄의 [지정일 등록] → 비우고 저장 → 내일 날짜로 저장 → 2026-07-01 로 저장</t>
+          <t>[＋ 직접 등록] → 이름 «남다슬_관리감독자» · 부서는 [조직도]에서 내 부서(건설과) · 구분 관리감독자 · 고용형태 공무원 → [등록]</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>빈 칸·미래 날짜는 막히고 과거 날짜는 «관리감독자 지정일을 저장했습니다.»</t>
+          <t>목록에 생기고 지정일은 비어 있다(지정일은 다음 줄에서 따로 넣는다)</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="51" customHeight="1">
+    <row r="8" ht="66" customHeight="1">
       <c r="A8" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>하정수</t>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -2136,31 +2133,32 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>지정일은 재난안전과만 넣는다</t>
+          <t>지정일 넣기 — 빈 칸·미래 날짜</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>① 관리감독자 줄을 본다
-② 등록 창에서 구분을 관리감독자로 골라 등록한다</t>
+          <t>4번 줄의 [지정일 등록] ① 비운 채 [저장]
+② 내일 날짜로 [저장]
+③ 오늘로 [저장]</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>[지정일 등록]이 없고, 관리감독자 등록은 «…재난안전과 담당자에게 요청하세요»로 막힌다</t>
+          <t>① 지정일을 넣으라는 안내가 뜨고 저장되지 않는다 ② 미래 날짜는 막힌다 — 저장되면 «실패»(미래 지정일은 이수 판정을 틀리게 한다) ③ 저장되고 지정일에 오늘이 보인다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="81" customHeight="1">
       <c r="A9" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>하정수</t>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -2170,30 +2168,32 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>부서 담당자의 등록 창</t>
+          <t>지정일은 재난안전과만 넣는다</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>[＋ 직접 등록]을 연다</t>
+          <t>① 4번의 «남다슬_관리감독자» 줄과 다른 관리감독자 줄을 본다
+② [＋ 직접 등록]에서 이름·채용일을 넣고 구분을 관리감독자로 골라 [등록]
+③ [취소]</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>부서 칸이 물순환사업소로 고정돼 있다</t>
+          <t>어느 줄에도 [지정일 등록]이 없다(지정일이 빈 줄은 «지정일은 재난안전과가 등록»). 등록 창의 지정일 칸은 입력할 수 없고 [등록]은 «…관리감독자 등록은 재난안전과 담당자에게 요청하세요.»로 막힌다</t>
         </is>
       </c>
       <c r="G9" s="29" t="n"/>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>박안전</t>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
@@ -2203,30 +2203,30 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>이름만 고치기</t>
+          <t>부서 담당자의 등록 창</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>QA_근로자01 [수정] → 이름만 바꿔 저장 → 다시 원래대로</t>
+          <t>[＋ 직접 등록]을 열어 부서 칸을 보고 [취소]</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>«근로자 정보 저장» — 손대지 않은 계약기간 때문에 막히지 않는다</t>
+          <t>부서 칸이 내 부서(건설과)로 고정돼 있고 [조직도] 버튼 없이 «소속 부서 명단에 등록합니다.»가 보인다</t>
         </is>
       </c>
       <c r="G10" s="29" t="n"/>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -2236,30 +2236,31 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>삭제는 한 번 더 묻는다</t>
+          <t>이름만 고치기</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>한 명을 더 등록 → 그 사람 [삭제] → 확인</t>
+          <t>① «남다슬_근로자01» [수정] → 이름 끝에 «_수정»을 붙여 [저장]
+② 다시 [수정] → 원래 이름으로 [저장]</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>확인 창을 거친 뒤 «근로자를 명단에서 제외했습니다.»</t>
+          <t>두 번 모두 «근로자 정보 저장» — 손대지 않은 계약기간 때문에 막히지 않는다</t>
         </is>
       </c>
       <c r="G11" s="29" t="n"/>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>하정수</t>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
@@ -2269,30 +2270,65 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>엑셀 업로드</t>
+          <t>삭제는 한 번 더 묻는다</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>[📥 엑셀 업로드] → [업로드]</t>
+          <t>① «남다슬_근로자02»를 등록한다(나머지는 기본값)
+② 그 줄 [삭제] → 확인 창 → [삭제]</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>창에 «목업» 같은 말이 없고 «예시 계약직 근로자 4명»을 알려 준 뒤 목록이 4명 늘어난다</t>
+          <t>확인 창(«…명단에서 제외합니다. 이력은 보존됩니다.»)을 거친 뒤 «근로자를 명단에서 제외했습니다.», 목록에서 사라진다</t>
         </is>
       </c>
       <c r="G12" s="29" t="n"/>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
     </row>
+    <row r="13" ht="81" customHeight="1">
+      <c r="A13" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>QA하정수2(담당 공무원)</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>안전보건교육 &gt; 근로자 명단 관리</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>엑셀 업로드</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>① [📥 엑셀 업로드] → 서식을 내려받아 칸 순서를 본다
+② 배포받은 «근로자 업로드 예시 남다슬.xlsx»를 골라 [업로드] (한 번만 — 다시 올리면 4명이 또 생긴다)</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>서식 칸이 부서명·이름·구분·고용형태·채용일·계약기간개월이다. 올리면 «남다슬_근로자A~D» 4명이 내 부서(건설과)로 목록에 생긴다. 예시 파일 칸이 서식과 달라 막히면 «문의»</t>
+        </is>
+      </c>
+      <c r="G13" s="29" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I12"/>
+  <autoFilter ref="A3:I13"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G12">
+  <conditionalFormatting sqref="G4:G13">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"성공"</formula>
     </cfRule>
@@ -2312,13 +2348,13 @@
       <formula>"문의"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H12">
+  <conditionalFormatting sqref="H4:H13">
     <cfRule type="expression" priority="7" dxfId="7">
       <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G4:G12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
+    <dataValidation sqref="G4:G13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
       <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2334,11 +2370,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -2358,7 +2394,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 앞 시트와 같은 탭에서 이어서 하세요. 재난안전과가 집합교육을 만들고 → 부서가 참석자를 내고 → 재난안전과가 종료합니다.</t>
+          <t>🗂 QA박안전2 창이 집합교육을 만들고(13·14번) → QA하정수2 창이 내 부서 참석자를 내고 → QA박안전2 창이 종료합니다. 14번 교육은 끝까지 진행 중으로 둡니다.</t>
         </is>
       </c>
     </row>
@@ -2411,11 +2447,11 @@
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2430,7 +2466,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>[집합교육] ↔ [자체교육(부서)]를 바꾸고 조건을 몇 개 건다</t>
+          <t>[집합교육] ↔ [자체교육 (부서)]를 바꾸고 조건을 몇 개 건다 → [필터 초기화]</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -2442,13 +2478,13 @@
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="51" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>하정수 → 홍길동</t>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -2463,12 +2499,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>집합교육 탭을 본다</t>
+          <t>[집합교육] 탭을 본다</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>하정수에게 [＋ 집합교육 등록]이 없고 «…재난안전과 담당자가 등록합니다»가 보인다. 홍길동은 조회 전용</t>
+          <t>[＋ 집합교육 등록]이 없고 «집합교육은 재난안전과 담당자가 등록합니다»가 보인다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
@@ -2477,11 +2513,11 @@
     </row>
     <row r="6" ht="51" customHeight="1">
       <c r="A6" s="28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -2496,25 +2532,26 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>[＋ 집합교육 등록] → 빈 채로 [등록] → 내용 QA_정기교육_집합 · 2026-07-20 14:00~16:00 · 강사 · 장소 → [등록]</t>
+          <t>① [＋ 집합교육 등록] → 빈 채로 [등록]
+② 내용 «남다슬_집합교육» · 일자 오늘 · 14:00~16:00 · 강사 · 장소를 넣고 [등록]</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>빈 채로는 «교육 내용을 입력하세요.» 등록하면 카드가 생기고 교육시간이 2h로 계산된다</t>
+          <t>빈 채로는 «교육 내용을 입력하세요.» 등록하면 «집합교육 등록 · 참석자 등록부 접수 개시», 카드가 생기고 시간이 2h로 계산된다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="66" customHeight="1">
+    <row r="7" ht="126" customHeight="1">
       <c r="A7" s="28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -2529,14 +2566,14 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>등록 창에서 ① 날짜를 5개까지 추가하고 한 번 더
-② 한 날의 끝 시각을 시작보다 이르게
-③ 고쳐서 2일짜리로 등록</t>
+          <t>[＋ 집합교육 등록]에서 ① 내용 «남다슬_집합교육_2일»을 먼저 넣고 [＋ 일자 추가]로 5일까지 늘린다
+② 한 회차의 종료 시각을 시작보다 이르게 하고 [등록]
+③ [이 일자 삭제]로 2일만 남기고, 남은 회차의 시각을 바르게(종료가 시작보다 뒤) 고쳐 [등록]</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>«최대 5일까지» 안내가 뜨고 끝이 시작보다 이르면 막힌다. 카드에 «…외 1일», 시간은 두 날의 합</t>
+          <t>5일이 되면 추가 버튼 자리에 «최대 5일»이 보인다. 종료가 시작보다 이르면 «…0h로 계산됩니다» 경고와 함께 [등록]이 «N회차의 일자·시작·종료 시각을 확인하세요…»로 막힌다. 등록하면 카드에 «…외 1일», 시간은 두 날의 합이다</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
@@ -2545,11 +2582,11 @@
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -2564,12 +2601,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>등록 창의 첨부 영역을 본다</t>
+          <t>[＋ 집합교육 등록] 창의 첨부 영역을 보고 [취소]</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>«참석자 명단 · 교육 자료» 두 칸이 있고 교육 사진 칸은 없다</t>
+          <t>«참석자 명단» · «교육 자료» 두 칸이 있고 교육 사진 칸은 없다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
@@ -2578,11 +2615,11 @@
     </row>
     <row r="9" ht="51" customHeight="1">
       <c r="A9" s="28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -2592,30 +2629,30 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>기존 교육을 그대로 저장</t>
+          <t>그대로 저장해도 막히지 않는다</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>«2026년 8월 정기 안전보건교육» [수정] → 아무것도 안 바꾸고 [저장]</t>
+          <t>13번 교육 카드의 [수정] → 아무것도 안 바꾸고 [저장]</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>끝 시각 17:00이 채워져 있고 «교육 정보를 저장했습니다 · 교육시간 3h»가 뜬다(저장이 막히면 실패)</t>
+          <t>종료 시각 16:00이 채워져 있고 «교육 정보를 저장했습니다 · 교육시간 2h»가 뜬다(저장이 막히면 실패)</t>
         </is>
       </c>
       <c r="G9" s="29" t="n"/>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
     </row>
-    <row r="10" ht="81" customHeight="1">
+    <row r="10" ht="66" customHeight="1">
       <c r="A10" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>하정수</t>
+        <v>17</v>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
@@ -2625,32 +2662,30 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>참석자 등록부 내기</t>
+          <t>예전에 등록된 교육의 수정 창</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>위 12번 교육 상세 → [＋ 참석자 등록부 등록] → ① 아무도 안 고르고
-② 2명 고르고 서명파일 없이
-③ 서명파일을 넣고 참석시간 3 → 2로 고쳐 [신청 완료]</t>
+          <t>서버에 처음부터 있던 집합교육(예: «2026년 8월 정기 안전보건교육») 카드의 [수정]을 열어 종료 시각만 보고 [취소] — 남의 교육이라 저장하지 않는다</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>빈 것마다 막히고, 마지막에 «물순환사업소 · 2명 신청 완료». 부서는 물순환사업소로 고정</t>
+          <t>종료 시각이 비어 있지 않고 시작 시각 + 교육시간으로 채워져 있다(8월 교육이면 17:00). 그런 교육이 없으면 «확인 불가»</t>
         </is>
       </c>
       <c r="G10" s="29" t="n"/>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="111" customHeight="1">
       <c r="A11" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>하정수</t>
+        <v>18</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -2660,17 +2695,20 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>같은 부서는 두 번 못 낸다</t>
+          <t>참석자 등록부 내기</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>같은 교육에 다시 등록부를 낸다</t>
+          <t>13번 교육 [상세 →] → [＋ 참석자 등록부 등록] ① 아무도 안 고르고 [신청 완료]
+② «남다슬_근로자01» 포함 2명을 고르고 서명파일 없이 [신청 완료]
+③ [＋ 서명파일 첨부] 후 실제 참석시간 3으로 [신청 완료]
+④ 2로 고쳐 [신청 완료]</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>«…이미 등록된 부서입니다 — 신청 취소 후 다시 등록하세요.»</t>
+          <t>부서는 내 부서(건설과)로 고정. ① «근로자를 1명 이상 선택하세요.» ② «서명파일을 업로드하세요 (필수).» ③ «실제 참석시간을 0보다 크고 교육 예정시간 이하로 입력하세요.»로 막히고 ④ «건설과 · 2명 신청 완료»</t>
         </is>
       </c>
       <c r="G11" s="29" t="n"/>
@@ -2679,11 +2717,11 @@
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>정환경</t>
+        <v>19</v>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
@@ -2693,30 +2731,30 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>다른 부서 담당자</t>
+          <t>같은 부서는 두 번 못 낸다</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>같은 교육 상세 → 환경과로 1명 신청 → 물순환사업소 줄을 본다</t>
+          <t>같은 상세에서 [＋ 참석자 등록부 등록] → 1명 고르고 서명파일 첨부 → [신청 완료]</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>환경과로 신청된다. 물순환사업소 줄에는 [등록 취소]가 없다</t>
+          <t>«…이미 등록된 부서입니다 — 신청 취소 후 다시 등록하세요.»가 뜨고 줄이 늘지 않는다</t>
         </is>
       </c>
       <c r="G12" s="29" t="n"/>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="81" customHeight="1">
       <c r="A13" s="28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA박안전2(재난안전과) → QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
@@ -2726,30 +2764,31 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>등록 취소하고 다시 내기</t>
+          <t>남의 부서 줄은 못 건드린다</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>자기 부서 줄 [등록 취소] → 확인 → 다시 2명 신청</t>
+          <t>① QA박안전2 창에서 13번 교육 상세 → [＋ 참석자 등록부 등록] → 부서 재난안전과(기본값) 그대로 1명 고르고 서명파일 첨부 → [신청 완료]
+② QA하정수2 창에서 같은 상세를 새로고침</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>«신청 내역과 서명파일이 삭제됩니다»를 확인한 뒤 줄어들고, 다시 신청된다</t>
+          <t>① «재난안전과 · 1명 신청 완료» ② QA하정수2 창의 재난안전과 줄에는 [신청 취소]가 없고 내 부서 줄에만 있다</t>
         </is>
       </c>
       <c r="G13" s="29" t="n"/>
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" ht="66" customHeight="1">
       <c r="A14" s="28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C14" s="30" t="inlineStr">
@@ -2759,30 +2798,31 @@
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>교육 종료 처리</t>
+          <t>신청 취소하고 다시 내기</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>위 12번 교육 상세 → [교육 종료 처리] → 확인</t>
+          <t>① 내 부서 줄 [신청 취소] → 확인 창 → [신청 취소]
+② 다시 «남다슬_근로자01» 포함 2명 · 서명파일 · 참석시간 2로 신청</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>창이 신청 부서·인원을 알려 주고 «교육 종료 · N명 카운트 완료», 상태가 완료로 바뀐다</t>
+          <t>확인 창이 «신청 내역과 서명파일이 삭제됩니다.»를 알리고 «건설과 신청을 취소했습니다.» 후 줄이 빠진다. 다시 신청하면 줄이 돌아온다</t>
         </is>
       </c>
       <c r="G14" s="29" t="n"/>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n"/>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="51" customHeight="1">
       <c r="A15" s="28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>하정수 → 홍길동</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
@@ -2792,17 +2832,17 @@
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>종료 처리는 재난안전과만</t>
+          <t>교육 종료 처리</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>진행 중인 다른 집합교육 상세를 본다</t>
+          <t>13번 교육 상세 → [교육 종료 처리] → 확인 창을 읽고 [종료 처리]</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>[교육 종료 처리]가 없다</t>
+          <t>확인 창이 «신청 2개 부서 · 3명»을 알려 주고, 종료하면 «교육 종료 · 3명 카운트 완료», 상태가 완료로 바뀐다</t>
         </is>
       </c>
       <c r="G15" s="29" t="n"/>
@@ -2811,11 +2851,11 @@
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C16" s="30" t="inlineStr">
@@ -2825,30 +2865,30 @@
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>종료 뒤 정정은 사유가 필요</t>
+          <t>종료 처리는 재난안전과만</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>20번에서 종료한 교육의 환경과 줄 등록 취소 → 사유 없이 → 사유 넣고</t>
+          <t>14번 교육(진행 중)의 상세를 본다</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>사유 없이는 막히고, «환경과 원 기록을 보존하고 취소이력을 남겼습니다.»</t>
+          <t>[교육 종료 처리]가 없다([＋ 참석자 등록부 등록]은 있다)</t>
         </is>
       </c>
       <c r="G16" s="29" t="n"/>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="51" customHeight="1">
       <c r="A17" s="28" t="n">
-        <v>23</v>
-      </c>
-      <c r="B17" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+        <v>24</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
@@ -2858,30 +2898,31 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>시간을 고치면 이수 기록도 바뀐다</t>
+          <t>종료 뒤 정정은 사유가 필요</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>20번 교육 [수정] → 끝 시각을 1시간 늘려 저장</t>
+          <t>13번 교육 상세의 재난안전과 줄 [완료기록 정정] ① 사유 없이 [취소이력 남기기]
+② 사유를 넣고 [취소이력 남기기]</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>«…교육시간 Nh · 이수기록 M건 갱신»</t>
+          <t>① «정정 사유를 입력하세요.» ② «재난안전과 원 기록을 보존하고 취소이력을 남겼습니다.» 줄은 지워지지 않고 «등록취소»와 사유가 남는다</t>
         </is>
       </c>
       <c r="G17" s="29" t="n"/>
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="51" customHeight="1">
       <c r="A18" s="28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
@@ -2891,30 +2932,65 @@
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>삭제는 지울 건수를 알려 준다</t>
+          <t>시간을 고치면 이수 기록도 바뀐다</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>집합교육을 하나 더 만들고 → 그 교육 [삭제] → 확인 창을 본다</t>
+          <t>13번 교육 카드 [수정] → 종료 시각을 16:00에서 17:00으로 → [저장]</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>확인 창이 지워질 신청·이수기록 건수를 알려 주고 지운다</t>
+          <t>«교육 정보를 저장했습니다 · 교육시간 3h · 이수기록 2건 갱신»(24번에서 정정한 재난안전과 몫은 빠진다)</t>
         </is>
       </c>
       <c r="G18" s="29" t="n"/>
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="7" t="n"/>
     </row>
+    <row r="19" ht="66" customHeight="1">
+      <c r="A19" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전2(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>안전보건교육 &gt; 현업근로자 &gt; 정기교육</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>삭제는 지울 건수를 알려 준다</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>① 집합교육 «남다슬_삭제용»을 등록
+② 그 카드의 [＋ 참석자 등록부 등록]으로 재난안전과 1명 신청
+③ [삭제] → 확인 창을 읽고 [삭제]</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>확인 창이 «신청 1개 부서 · 1명 신청 내역이 함께 삭제됩니다.»를 알리고, 삭제하면 «교육을 삭제했습니다 · 신청 1건 · 이수기록 0건 회수»</t>
+        </is>
+      </c>
+      <c r="G19" s="29" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I18"/>
+  <autoFilter ref="A3:I19"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G18">
+  <conditionalFormatting sqref="G4:G19">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"성공"</formula>
     </cfRule>
@@ -2934,13 +3010,13 @@
       <formula>"문의"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H18">
+  <conditionalFormatting sqref="H4:H19">
     <cfRule type="expression" priority="7" dxfId="7">
       <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G4:G18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
+    <dataValidation sqref="G4:G19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
       <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2960,7 +3036,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -2980,7 +3056,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 앞 시트와 같은 탭에서 이어서 하세요.</t>
+          <t>🗂 자체·기타 교육은 각 부서가 등록합니다. 대상자는 1번 시트에서 만든 내 근로자를 고릅니다.</t>
         </is>
       </c>
     </row>
@@ -3031,13 +3107,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="51" customHeight="1">
+    <row r="4" ht="81" customHeight="1">
       <c r="A4" s="28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3052,12 +3128,14 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>[자체교육(부서)] → [＋ 자체교육 등록·진행] → 대상자 없이 → 내용 없이 → 다 채워서(QA_정기교육_자체, 대상자 2명, 증빙) 저장</t>
+          <t>[자체교육 (부서)] → [＋ 자체교육 등록·진행] ① 아무것도 안 넣고 [진행 처리]
+② 내용 «남다슬_자체교육»만 넣고 [진행 처리]
+③ 시각 08:00~18:00 · 대상자 «남다슬_근로자01»·남다슬_근로자C · 증빙을 넣고 [진행 처리]</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>빈 칸이면 막히고 저장하면 목록에 생긴다. 부서는 물순환사업소로 고정</t>
+          <t>① «교육 내용을 입력하세요.» ② «교육 대상자를 1명 이상 선택하세요.» ③ «건설과 자체교육 완료 · 10h · 2명 카운트», 목록에 생긴다. 부서는 내 부서(건설과)로 고정</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
@@ -3066,11 +3144,11 @@
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="28" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -3085,7 +3163,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>등록 창의 첨부 영역을 본다</t>
+          <t>자체교육 등록 창의 첨부 영역을 보고 [취소]</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -3099,11 +3177,11 @@
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3118,25 +3196,25 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>[전체] · [미이수] · [이수] 탭을 본다</t>
+          <t>[전체] · [미이수] · [이수] 탭을 보고 [미이수]에서 «남다슬_근로자01»을 검색한다</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>탭이 셋이고(«교육 건» 탭 없음) QA_근로자01이 미이수에 있다</t>
+          <t>탭이 셋이고(«교육 건» 탭 없음) «남다슬_근로자01» 줄이 미이수에 있다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="51" customHeight="1">
+    <row r="7" ht="66" customHeight="1">
       <c r="A7" s="28" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -3151,25 +3229,25 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>목록의 필요시간을 본다</t>
+          <t>목록의 고용형태·필요시간·상태를 본다</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>고용형태·계약기간대로 1h · 4h · 8h이고 상태가 미이수 · 정상 이수 · 지연 이수 · 판정 불가로 나뉜다</t>
+          <t>필요시간이 일용·1주 이하 1h · 1개월 이하 4h · 그 밖 8h 규칙대로다(«남다슬_근로자01»은 기간제 6개월이라 8h). 상태는 미이수 · 정상 이수 · 지연 이수 중 하나다</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="51" customHeight="1">
+    <row r="8" ht="126" customHeight="1">
       <c r="A8" s="28" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -3184,25 +3262,27 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>[＋ 채용시 교육 추가] → 대상자 없이 → QA_근로자01만 고르고 증빙 없이 → 증빙 넣고 [교육기록 등록]</t>
+          <t>[＋ 채용시 교육 추가] ① 대상자 없이 [교육기록 등록]
+② 대상자 부서를 내 부서(건설과)로 거르고 «남다슬_근로자01»만 체크, 시각 09:00~17:00, 내용 «남다슬_채용시교육» → 증빙 없이 [교육기록 등록]
+③ «교육일지 및 교육사진 등» 칸에 파일을 넣고 [교육기록 등록]</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>빈 칸이면 막히고, 등록하면 «1명 교육기록 등록…» 후 이수 탭으로 옮겨 간다</t>
+          <t>① «교육 대상자를 1명 이상 선택하세요.» ② «교육일지 및 교육사진 등 증빙을 첨부하세요.» ③ «1명 교육기록 등록 · 이수 완료 1명» 후 [이수] 탭으로 옮겨 가고 상태가 정상 이수다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="141" customHeight="1">
       <c r="A9" s="28" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -3217,25 +3297,29 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>미이수 2명 체크 → [선택 교육기록 등록] → 교육일 없이 → 증빙 없이 → 채워서</t>
+          <t>[미이수] 탭 ① 아무도 체크하지 않고 [선택 교육기록 등록 (0)]
+② 부서 조건을 내 부서(건설과)로 걸고 10번의 남다슬_근로자A·남다슬_근로자B을 체크 → [선택 교육기록 등록 (2)]
+③ 실제 교육일을 비우고 [교육기록 등록]
+④ 교육일을 오늘로, 증빙 없이 [교육기록 등록]
+⑤ 증빙 파일을 골라 [교육기록 등록]</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>빈 칸이면 막히고, 등록하면 «2명 소급 교육기록 등록…»</t>
+          <t>① «미이수자를 1명 이상 선택하세요.» ③ «실제 교육일을 입력하세요.» ④ «교육일지·서명부 증빙을 선택하세요.» ⑤ «2명 소급 교육기록 등록 · 이수 완료 2명 · 교육 건 2건 생성»</t>
         </is>
       </c>
       <c r="G9" s="29" t="n"/>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
     </row>
-    <row r="10" ht="51" customHeight="1">
+    <row r="10" ht="66" customHeight="1">
       <c r="A10" s="28" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
@@ -3250,12 +3334,13 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>29번 이수자 [이수 수정] → 날짜 바꿔 저장 → 다시 [이수 수정] → [이수 기록 삭제] → [이수 취소]</t>
+          <t>31번 «남다슬_근로자01» 줄 ① [이수 수정] → 이수일을 어제로 [저장]
+② 다시 [이수 수정] → [이수 기록 삭제] → 확인 창 → [이수 취소]</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>«이수일을 수정했습니다 — 날짜», 삭제하면 «이수기록 N건 회수 · 미이수로 되돌렸습니다»</t>
+          <t>① «이수일을 수정했습니다 — (어제 날짜)» ② 확인 창이 회수될 시간을 알려 주고 «이수기록 1건 회수 · 미이수로 되돌렸습니다…», 다시 [미이수]에 있다</t>
         </is>
       </c>
       <c r="G10" s="29" t="n"/>
@@ -3264,11 +3349,11 @@
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -3278,7 +3363,7 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>자기 부서만 보인다</t>
+          <t>내 부서만 보인다</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -3288,20 +3373,20 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소 사람만 보이고 부서 조건에도 물순환사업소만 있다</t>
+          <t>내 부서(건설과) 사람만 보이고 부서 조건에도 내 부서만 있다</t>
         </is>
       </c>
       <c r="G11" s="29" t="n"/>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
     </row>
-    <row r="12" ht="66" customHeight="1">
+    <row r="12" ht="96" customHeight="1">
       <c r="A12" s="28" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -3316,25 +3401,25 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>목록을 본다</t>
+          <t>[전체] 탭과 [미이수]·[이수] 탭을 차례로 본다</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>지정일 없는 사람은 «판정 불가»이고 미이수·이수 어느 탭에도 없다. «전체 = 미이수 + 이수 + 판정 불가» 안내가 있고, 4번에서 지정일을 넣은 사람만 판정된다</t>
+          <t>위 안내에 «지정일이 등록되지 않은 사람은 '판정 불가'…»가 있다. 지정일 없는 사람은 «판정 불가 — 지정일 미등록»이고 [미이수]·[이수] 어느 탭에도 없다(그래서 전체 숫자가 미이수 + 이수보다 크다). 4번의 «남다슬_관리감독자»는 [미이수]에 있다</t>
         </is>
       </c>
       <c r="G12" s="29" t="n"/>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
     </row>
-    <row r="13" ht="51" customHeight="1">
+    <row r="13" ht="111" customHeight="1">
       <c r="A13" s="28" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3349,25 +3434,27 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>[＋ 기타 교육 등록·진행] → 빈 채로 [진행 처리] → 유형 «작업내용 변경 시» → 대상자 없이 → 다 채우고 시간 0.5</t>
+          <t>[＋ 기타 교육 등록·진행] ① 빈 채로 [진행 처리]
+② 교육 분류 «작업내용 변경 시 교육» · 부서는 [조직도]에서 내 부서(건설과) · 내용 «남다슬_기타교육»을 넣고 대상자 없이 [진행 처리]
+③ «남다슬_근로자01»을 체크하고 교육 시간 0.5로 [진행 처리]</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>빈 칸이면 막힌다. 유형을 고르면 법정 최소 시간과 근거가 보이고, 모자라도 등록되며 «법정 최소 미달 N명»이 뜬다</t>
+          <t>① «일자·시각·시간·내용을 모두 입력하세요.» 분류를 고르면 법정 최소 교육시간(1시간 · 2시간)과 근거가 보인다. ② «대상자를 1명 이상 선택하세요.» ③ 막지 않고 «작업내용 변경 시 교육 진행 완료 · 1명 · 법정 최소 미달 1명», 카드에 «법정 최소 미달 1명»</t>
         </is>
       </c>
       <c r="G13" s="29" t="n"/>
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
     </row>
-    <row r="14" ht="51" customHeight="1">
+    <row r="14" ht="126" customHeight="1">
       <c r="A14" s="28" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C14" s="30" t="inlineStr">
@@ -3382,25 +3469,27 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>유형 «특별교육» → 대상 작업 없이 진행 → 두 개 고르기 → «기타 — 법령 매핑 대기»를 내용 없이 진행</t>
+          <t>① 분류 «특별교육» · 부서는 [조직도]에서 내 부서(건설과) · 내용 «남다슬_특별교육» · 대상자 «남다슬_근로자01» → 대상 작업 없이 [진행 처리]
+② 대상 작업 두 개와 «기타 — 목록에 없어 법령 매핑이 필요한 작업»을 체크하고 그 칸을 그대로 둔 채 [진행 처리]
+③ 기타 칸에 내용을 적고 [진행 처리]</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>대상 작업이 없으면 막히고 여러 개 고를 수 있다. «기타»는 내용을 적어야 저장된다</t>
+          <t>① «특별교육 대상 작업을 1건 이상 선택하세요.» ② «기타 대상 작업 내용을 입력하세요.» ③ «특별교육 진행 완료 · 1명 카운트», 카드에 «대상 작업 3건». 여러 개를 함께 고를 수 있다</t>
         </is>
       </c>
       <c r="G14" s="29" t="n"/>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n"/>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="51" customHeight="1">
       <c r="A15" s="28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -3415,25 +3504,25 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>등록 창의 유형 목록을 현업근로자 쪽과 비교한다</t>
+          <t>등록 창의 교육 분류 목록과 법정 시간을 36번(현업근로자) 창과 비교하고 [취소]</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>«건설업 기초»가 없고 작업내용 변경 2h · 특별교육 16h 한 가지 기준이다</t>
+          <t>«건설업 기초안전보건교육»이 없고, 작업내용 변경 시 교육은 관리감독자 2시간 · 특별교육은 관리감독자 16시간 한 가지 기준이다</t>
         </is>
       </c>
       <c r="G15" s="29" t="n"/>
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="96" customHeight="1">
       <c r="A16" s="28" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -3443,30 +3532,33 @@
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>자기 부서 교육만 고친다</t>
+          <t>내 부서 교육만 고친다</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>자기 부서 교육(없으면 하나 등록) [수정]·[삭제] → 다른 부서 교육을 본다</t>
+          <t>① [＋ 기타 교육 등록·진행] → 내용 «남다슬_기타교육_부서» · 대상자 남다슬_근로자D · 시간 2 → [진행 처리]
+② 그 카드 [수정] → 시간 3 → [저장]
+③ 그 카드 [삭제] → 확인 창 → [삭제]
+④ 다른 부서 카드를 본다</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>자기 부서 것만 고칠 수 있고, 삭제 창이 지워질 이수기록 건수를 알려 준다</t>
+          <t>부서는 내 부서(건설과)로 고정. ② «기타 교육 정보를 저장했습니다 · 이수기록 1건 갱신.» ③ 확인 창이 «대상자 1명에게 반영된 이수시간 3h 도 함께 회수»를 알리고 «기타 교육을 삭제했습니다 · 이수기록 1건 회수» ④ 다른 부서 카드에는 [수정]·[삭제]가 없다</t>
         </is>
       </c>
       <c r="G16" s="29" t="n"/>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="51" customHeight="1">
       <c r="A17" s="28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3476,17 +3568,17 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>관리감독자 정기교육</t>
+          <t>관리감독자 정기교육 대상자</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>등록 창의 대상자 목록을 본다</t>
+          <t>[자체교육 (부서)] → [＋ 자체교육 등록·진행] → 부서를 [조직도]에서 내 부서(건설과)로 바꿔 대상자 목록을 보고 [취소]</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>관리감독자만 대상자로 나온다</t>
+          <t>관리감독자만 대상자로 나온다 — 4번의 «남다슬_관리감독자»는 있고 «남다슬_근로자01»은 없다</t>
         </is>
       </c>
       <c r="G17" s="29" t="n"/>
@@ -3545,7 +3637,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -3565,7 +3657,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 앞 시트와 같은 탭에서 이어서 하세요. 2·3번 시트에서 끝낸 교육이 여기 모입니다.</t>
+          <t>🗂 2·3번 시트에서 끝낸 교육이 여기 모입니다. 독촉은 내 부서 사람에게만 합니다.</t>
         </is>
       </c>
     </row>
@@ -3616,13 +3708,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="28" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3637,12 +3729,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소 줄 [상세]</t>
+          <t>[부서별 요약]에서 내 부서(건설과) 줄의 대상·완료 인원을 보고 [상세]</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>대상·완료 인원과 완료율이 상세 목록과 맞다</t>
+          <t>요약의 대상 인원이 상세 목록 인원과, 완료 인원이 상세의 «완료» 수와 같다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
@@ -3651,11 +3743,11 @@
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="28" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -3670,25 +3762,25 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대상이 0명인 부서를 찾는다</t>
+          <t>구분 조건을 «판매»로 걸고 대상 인원이 0명인 부서 줄을 본다 → [필터 초기화]</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>0%가 아니라 «대상 없음»으로 보인다(그런 부서가 없으면 «확인 불가»)</t>
+          <t>0명인 부서의 완료율이 0%가 아니라 «대상 없음»이다. 0명인 부서가 없으면 «확인 불가»</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -3703,25 +3795,25 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>집합(20번)과 자체(25번)를 모두 들은 사람의 필요·인정·미달을 본다</t>
+          <t>[대상자별 상세]에서 «남다슬_근로자01»을 검색해 필요·인정·미달·정기를 본다</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>인정 = 집합 + 자체, 미달 = 필요 − 인정이고 음수가 없다</t>
+          <t>필요 12h · 인정 13h(13번 집합 3h + 27번 자체 10h) · 미달 0h(음수가 아니다) · 정기 «완료»</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="28" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -3736,25 +3828,25 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>부서·구분·고용형태·이수 상태를 함께 건다 → [필터 초기화]</t>
+          <t>[대상자별 상세]에서 부서·구분·고용형태·이수 상태를 함께 건다 → [필터 초기화]</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>조건대로 걸러지고 초기화하면 전체로 돌아온다</t>
+          <t>조건대로 걸러지고 위 «조회 대상 …» 표시가 건 구분·고용형태를 보여 준다. 초기화하면 전체로 돌아온다</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="28" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -3769,25 +3861,25 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>부서별 요약을 본다</t>
+          <t>[부서별 요약]을 본다</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>자기 부서 줄에만 [상세]가 있고 다른 줄은 «—»다(버튼이 있는데 누르면 거절되면 실패)</t>
+          <t>내 부서 줄에만 [상세]가 있고 다른 줄은 «—»다(버튼이 있는데 누르면 거절되면 실패). 다른 부서의 합계 숫자는 보인다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
     </row>
-    <row r="9" ht="51" customHeight="1">
+    <row r="9" ht="96" customHeight="1">
       <c r="A9" s="28" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -3802,12 +3894,14 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>체크 없이 [일괄 독촉] → 2명 체크 → [일괄 독촉 (2)] → [독촉 발송] → [📜 독촉 이력]</t>
+          <t>[대상자별 상세] ① 아무도 체크하지 않고 [일괄 독촉 (0)]
+② 부서를 내 부서(건설과)로 걸고 10번의 남다슬_근로자A·남다슬_근로자B을 체크 → [일괄 독촉 (2)] → [독촉 발송]
+③ [📜 독촉 이력]</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>체크가 없으면 막힌다. 발송하면 «…2명 독촉 알림 기록 완료 (실제 문자·메일 미발송)» 후 이력에 남는다</t>
+          <t>① «미이수자를 1명 이상 선택하세요.» ② «1개 부서, 2명 독촉 알림 기록 완료 (실제 문자·메일 미발송)» ③ 이력에 내 부서 2명 줄이 있고 발신이 내 QA박안전2 계정 이름이다</t>
         </is>
       </c>
       <c r="G9" s="29" t="n"/>
@@ -3816,11 +3910,11 @@
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="28" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
@@ -3835,12 +3929,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>완료한 사람의 확인서 [발급]</t>
+          <t>43번의 «남다슬_근로자01» 줄 [발급]</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>보고서·제증명 화면이 그 사람으로 채워져 열린다</t>
+          <t>보고서·제증명 화면이 열리고 발급 대상자에 «남다슬_근로자01 · 건설과»가 채워져 있다</t>
         </is>
       </c>
       <c r="G10" s="29" t="n"/>
@@ -3899,7 +3993,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -3919,7 +4013,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 앞 시트와 같은 탭에서 이어서 하세요. 교육 공문은 결재 결과를 받지 않습니다 — 상태는 «결재중» 하나입니다.</t>
+          <t>🗂 적힌 순서대로 합니다 — 49번(QA하정수2)은 13번 교육 공문을 올리기 전에 봅니다. 상신하면 바로 «결재완료»(내부 처리)로 끝납니다. 검토·결재에 넣을 다른 두 사람의 박안전 계정은 단체방에서 미리 정해 둡니다.</t>
         </is>
       </c>
     </row>
@@ -3972,11 +4066,11 @@
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="28" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3991,25 +4085,25 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>진행 중인 교육과 20번(종료) 교육의 [공문 기안]을 본다</t>
+          <t>14번(진행 중)과 13번(종료) 교육 카드를 비교한다</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>진행 중인 교육은 «교육 종료 처리 후에 기안할 수 있습니다.», 종료된 교육은 기안된다</t>
+          <t>진행 중인 14번 카드에는 [공문 기안]이 없고, 종료된 13번 카드에만 [공문 기안]이 있다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="66" customHeight="1">
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="28" t="n">
-        <v>47</v>
-      </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+        <v>49</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -4019,30 +4113,31 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>공문 쓰기 → 미리보기 → 상신</t>
+          <t>공문은 교육을 등록한 부서가 쓴다</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>20번 교육 [공문 기안] → 제목을 지우고 미리보기 → 본문 없이 미리보기 → 본문 쓰기(칩 사용)·붙임 고르기 → [문서 미리보기 →] → [온나라로 결재 상신] → [상신]</t>
+          <t>① 27번 자체교육 카드
+② 13번 집합교육 카드를 본다(누르지 않는다)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>제목·본문이 없으면 막힌다. 기안 화면에 상신 버튼이 없고 붙임은 올려 둔 파일에서만 고른다. 상신하면 문서번호가 붙고 «결재중»</t>
+          <t>27번 카드에는 [공문 기안]이 있다. 13번 카드에는 버튼 대신 «여러 부서를 묶은 건이라 재난안전과 담당자가 기안합니다.»가 보인다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="51" customHeight="1">
+    <row r="6" ht="141" customHeight="1">
       <c r="A6" s="28" t="n">
-        <v>48</v>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+        <v>50</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -4052,30 +4147,33 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>결재선</t>
+          <t>결재선 — 같은 사람을 두 번 못 넣는다</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>검토·결재에 같은 사람을 넣어 본다 → 기안자 본인을 넣어 본다 → 검토 칸을 비우고 상신해 본다</t>
+          <t>13번 교육 [공문 기안] ① 결재 [조직도]에서 단체방에서 정한 결재 담당 박안전 계정(내 번호가 아닌 것)을 고른다
+② 검토 [조직도]를 열어 내 이름과 ①의 사람을 찾는다
+③ [＋ 검토]로 빈 칸을 더하고 본문을 한 줄 쓴 뒤 [문서 미리보기 →]
+④ [← 수정] → 더한 칸 [×] → [닫기](상신하지 않는다)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>고를 수 없게 흐리게 보이고, 칸이 비면 상신이 막힌다</t>
+          <t>② 내 이름은 «기안자», ①의 사람은 «결재 지정됨»으로 흐리게 나와 고를 수 없다 ③ 결재선 아래 «결재선을 확인하세요»가 뜨고, 미리보기에는 [온나라로 결재 상신] 대신 «지정하지 않은 단계가 …건 있습니다…»가 나온다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="186" customHeight="1">
       <c r="A7" s="28" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -4085,17 +4183,21 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>상신 뒤에는 잠긴다</t>
+          <t>공문 쓰기 → 미리보기 → 상신</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>그 교육 [수정]·[삭제] → 상세의 [등록 취소]</t>
+          <t>13번 교육 [공문 기안] ① 제목을 지우고 [문서 미리보기 →]
+② 제목을 «2026년 안전보건교육 실시 결과 보고 — 남다슬_집합교육»으로 다시 넣고 본문 없이 [문서 미리보기 →]
+③ 본문을 직접 쓰고(삽입 조각도 눌러 본다) 붙임을 체크한다
+④ 결재선 검토·결재에 단체방에서 정한 다른 두 사람의 박안전 계정을 고른다 — 처음 채워져 있는 기본값(실제 직원)은 반드시 바꾼다
+⑤ [문서 미리보기 →] → [온나라로 결재 상신] → [상신]</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>셋 다 잠겨 있다(등록 취소까지 잠겨야 성공)</t>
+          <t>① «공문 제목을 입력하세요.» ② «공문 본문을 입력하세요.» 기안 창에는 상신 버튼이 없고 붙임은 올려 둔 파일에서 체크만 한다(새로 올리는 칸 없음). 상신하면 바로 «결재완료»가 되고 «내부 처리»로 표시된다</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
@@ -4104,11 +4206,11 @@
     </row>
     <row r="8" ht="51" customHeight="1">
       <c r="A8" s="28" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -4118,17 +4220,18 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>잠금 안내 문구</t>
+          <t>상신 뒤에는 잠긴다</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>49번에서 뜬 안내를 읽는다</t>
+          <t>① 13번 교육 카드의 [수정]·[삭제] 자리를 본다
+② 상세 → 신청현황의 내 부서 줄을 본다</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>잠긴 이유(결재중)를 말하고, 이 시스템에서 할 수 없는 일(«반려 후 다시 시도»)을 권하지 않는다</t>
+          <t>카드에 [수정]·[삭제] 대신 잠금(🔒) 표시만 있고, 상세의 내 부서 줄도 잠겨 있다(정정까지 잠겨야 성공). [＋ 정정 등록부 추가]도 없다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
@@ -4137,11 +4240,11 @@
     </row>
     <row r="9" ht="51" customHeight="1">
       <c r="A9" s="28" t="n">
-        <v>51</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>하정수 → 홍길동</t>
+        <v>53</v>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -4151,30 +4254,30 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>공문은 교육을 등록한 부서가 쓴다</t>
+          <t>잠금 안내 문구</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>하정수: 25번 자체교육과 재난안전과 집합교육의 [공문 기안]을 본다 / 홍길동: 같은 화면</t>
+          <t>52번에서 연 상세의 잠금 안내와 교육 카드의 잠금 버튼 설명(마우스를 올리면 나온다)을 읽는다</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>하정수는 자기 부서 교육만 기안하고 나머지는 누가 기안하는지 안내된다. 홍길동에게는 기안 버튼이 없다</t>
+          <t>잠긴 이유(공문이 결재된 교육)를 알려 준다</t>
         </is>
       </c>
       <c r="G9" s="29" t="n"/>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>박안전</t>
+        <v>54</v>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -4189,25 +4292,25 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>이수 줄에서 공문으로 가는 연결을 본다</t>
+          <t>[이수] 탭에서 부서 조건을 내 부서(건설과)로 걸고 32번의 남다슬_근로자A 줄 [공문 기안] → 창 제목을 보고 [닫기](상신하지 않는다)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>그 사람이 들은 교육 건의 [공문 기안]으로 간다</t>
+          <t>남다슬_근로자A이 들은 교육 건의 공문 기안 창이 열린다(창 제목 끝이 «· 남다슬_근로자A»)</t>
         </is>
       </c>
       <c r="G10" s="29" t="n"/>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
     </row>
-    <row r="11" ht="51" customHeight="1">
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="28" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -4222,12 +4325,13 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>목록 → 조건 → 문서를 연다</t>
+          <t>① 검색창에 «남다슬_집합교육»을 친다
+② 그 줄의 [문서]를 누른다</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>47번 공문이 문서번호와 함께 있고 열린다. 승인·반려 버튼은 없고 «온나라에서 문서번호로 확인» 안내가 있다</t>
+          <t>51번 공문이 결재완료 · «내부 처리»로 있고 [문서]로 열린다. 승인·반려 버튼은 없다</t>
         </is>
       </c>
       <c r="G11" s="29" t="n"/>
@@ -4282,11 +4386,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -4299,14 +4403,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>안전보건교육 — 6 계정별 차이</t>
+          <t>안전보건교육 — 6 부서 담당자·다시 로그인</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 5번 시트까지 쓰던 탭에서 계정만 바꿔 가며 보세요. 58번(단계별 안내)만 새 탭에서 합니다.</t>
+          <t>🗂 QA하정수2 창에서 내 부서 화면을 보고, 마지막으로 로그인이 끊긴 뒤 다시 들어오는 것을 봅니다.</t>
         </is>
       </c>
     </row>
@@ -4357,178 +4461,115 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="66" customHeight="1">
       <c r="A4" s="28" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>김담양</t>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>안전보건교육 (9개 화면 전부)</t>
+          <t>안전보건교육 (자체·기타·채용시 등록 창)</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>군수는 보기만</t>
+          <t>부서 칸 고정</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>교육 메뉴 9개를 차례로 연다</t>
+          <t>① 정기교육 [자체교육 (부서)] 등록 창
+② 기타 교육 등록 창
+③ 채용시교육 [＋ 채용시 교육 추가] 창을 차례로 열어 보고 [취소]</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>등록·수정·삭제·종료·공문 버튼이 하나도 없고 화면 오류가 없다</t>
+          <t>①② 부서가 내 부서(건설과)로 고정돼 있고 [조직도]가 없다 ③ 대상자 목록에 내 부서 사람만 있다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="66" customHeight="1">
       <c r="A5" s="28" t="n">
-        <v>55</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>홍길동</t>
+        <v>57</v>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>QA하정수2(담당 공무원)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>안전보건교육 (현업근로자 3개 화면)</t>
+          <t>대시보드 &gt; 내 할일</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>과장은 보기만</t>
+          <t>교육 할 일 카드</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>정기교육·채용시교육·기타 교육을 연다</t>
+          <t>① «남다슬_집합교육_2일 — 참석자 등록부 등록 필요» 카드의 [신청하러 가기]
+② 뒤로 돌아와 «… — 안전보건교육 미이수 (독촉)» 카드를 찾는다</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>등록·종료·공문 버튼이 없고 조회 전용 안내가 보인다</t>
+          <t>① 목록이 아니라 14번 교육의 상세로 바로 간다 ② 46번에서 독촉한 남다슬_근로자A·남다슬_근로자B 카드가 있다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="28" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA박안전2(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>안전보건교육 (등록 창)</t>
+          <t>안전보건교육 &gt; 현업근로자 &gt; 정기교육</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>부서 칸 고정</t>
+          <t>로그인이 끊긴 뒤</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>자체교육·기타 교육·채용시 교육 추가 창을 차례로 연다</t>
+          <t>등록 창에 값을 적은 채 로그인 시간(30분)이 끝나기를 기다렸다가 저장을 눌러 본다 → 다시 로그인</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>부서가 물순환사업소로 고정돼 있다</t>
+          <t>로그인하라는 화면으로 가고 오류 창이 뜨지 않는다. 다시 로그인하면 교육 화면을 이어서 쓸 수 있다(적던 값이 사라지는 것은 메모)</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="28" t="n">
-        <v>57</v>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>하정수</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>대시보드 &gt; 내 할일</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>교육 할 일 카드</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>«…참석자 등록부 등록 필요» 카드를 누른다</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>목록이 아니라 그 교육의 상세로 바로 간다</t>
-        </is>
-      </c>
-      <c r="G7" s="29" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="28" t="n">
-        <v>58</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>안전보건교육 &gt; 현업근로자 &gt; 정기교육</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>단계별 안내</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>새 탭 → «단계별 안내 시작» → 끝까지 따라간다</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>단계마다 눌러야 할 버튼을 짚고 처리하면 다음 단계로 넘어간다</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:I8"/>
+  <autoFilter ref="A3:I6"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G8">
+  <conditionalFormatting sqref="G4:G6">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"성공"</formula>
     </cfRule>
@@ -4548,13 +4589,13 @@
       <formula>"문의"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H8">
+  <conditionalFormatting sqref="H4:H6">
     <cfRule type="expression" priority="7" dxfId="7">
       <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G4:G8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
+    <dataValidation sqref="G4:G6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
       <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4640,7 +4681,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
